--- a/data/credit_bond_all_2026-10-27.xlsx
+++ b/data/credit_bond_all_2026-10-27.xlsx
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ97"/>
+  <dimension ref="A1:AZ98"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4300/1.4200</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1429,7 +1429,11 @@
           <t>8+</t>
         </is>
       </c>
-      <c r="X6" s="3"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>1.78%~1.82%</t>
+        </is>
+      </c>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
@@ -1607,7 +1611,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6500/1.6400</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
@@ -1821,7 +1825,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7500/--</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -2049,7 +2053,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7800/--</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -2305,7 +2309,7 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>2.05%~2.15%</t>
+          <t>2.30%~2.40%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -2431,7 +2435,9 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AZ10" s="3"/>
+      <c r="AZ10" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
@@ -2483,7 +2489,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5025/1.4800</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -2523,7 +2529,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X11" s="3"/>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>1.49%~1.59%</t>
+        </is>
+      </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2743,7 +2753,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X12" s="3"/>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>1.63%~1.73%</t>
+        </is>
+      </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -2919,7 +2933,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5075/1.5050</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -2959,7 +2973,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X13" s="3"/>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>1.49%~1.59%</t>
+        </is>
+      </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3096,7 +3114,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C14" s="3"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>012682549.IB</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>0.24Y</t>
@@ -3175,7 +3197,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X14" s="3"/>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>1.42%~1.46%</t>
+        </is>
+      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3312,7 +3338,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>102684278.IB</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -3351,7 +3381,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.7600/--</t>
+          <t>1.6500/1.6400</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -3391,7 +3421,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X15" s="3"/>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3528,7 +3562,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C16" s="3"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>102684281.IB</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -3567,7 +3605,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7200/1.6500</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -3607,7 +3645,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X16" s="3"/>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>1.57%~1.67%</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -3744,7 +3786,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C17" s="3"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>042680357.IB</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
           <t>0.99Y</t>
@@ -3783,7 +3829,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4600/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -3823,7 +3869,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X17" s="3"/>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>1.42%~1.46%</t>
+        </is>
+      </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3964,7 +4014,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>042680356.IB</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
           <t>0.99Y</t>
@@ -4003,7 +4057,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4600/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -4043,7 +4097,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X18" s="3"/>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>1.42%~1.46%</t>
+        </is>
+      </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -4184,7 +4242,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C19" s="3"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>102684286.IB</t>
+        </is>
+      </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -4263,7 +4325,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="X19" s="3"/>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>1.57%~1.67%</t>
+        </is>
+      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -4406,7 +4472,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C20" s="3"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>042680358.IB</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
           <t>1Y</t>
@@ -4445,7 +4515,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4900/1.4577</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -4485,7 +4555,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X20" s="3"/>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>1.50%~1.54%</t>
+        </is>
+      </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -4622,7 +4696,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>102684295.IB</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -4701,7 +4779,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X21" s="3"/>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>1.55%~1.65%</t>
+        </is>
+      </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -4829,7 +4911,9 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AZ21" s="3"/>
+      <c r="AZ21" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
@@ -4842,7 +4926,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C22" s="3"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>102684289.IB</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -4921,7 +5009,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X22" s="3"/>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>2.83%~2.93%</t>
+        </is>
+      </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -5062,7 +5154,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C23" s="3"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>102684277.IB</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -5141,7 +5237,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X23" s="3"/>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>2.54%~2.64%</t>
+        </is>
+      </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -5282,7 +5382,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C24" s="3"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>102684285.IB</t>
+        </is>
+      </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -5321,7 +5425,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>1.7000/1.6200</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -5361,7 +5465,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X24" s="3"/>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -5485,7 +5593,9 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AZ24" s="3"/>
+      <c r="AZ24" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
@@ -5537,7 +5647,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5500/1.5300</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -5577,7 +5687,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X25" s="3"/>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>1.51%~1.61%</t>
+        </is>
+      </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -5706,7 +5820,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26常纺MTN001(科创债)</t>
+          <t>26常山北明MTN001(科创债)</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -5714,7 +5828,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C26" s="3"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>102684280.IB</t>
+        </is>
+      </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
           <t>2Y</t>
@@ -5918,7 +6036,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26中建钢构MTN001</t>
+          <t>26中建科工MTN001</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -5926,7 +6044,11 @@
           <t>10-28 18:00</t>
         </is>
       </c>
-      <c r="C27" s="3"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>102684307.IB</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
           <t>3+N</t>
@@ -5965,7 +6087,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7900/1.7300</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -6005,7 +6127,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X27" s="3"/>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>1.70%~1.80%</t>
+        </is>
+      </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -6133,7 +6259,9 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="AZ27" s="3"/>
+      <c r="AZ27" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
@@ -6146,7 +6274,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C28" s="3"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>102690093.IB</t>
+        </is>
+      </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
           <t>3+N</t>
@@ -6185,7 +6317,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5900/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -6221,7 +6353,11 @@
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>1.64%~1.74%</t>
+        </is>
+      </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6362,7 +6498,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C29" s="3"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>012682550.IB</t>
+        </is>
+      </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
           <t>0.16Y</t>
@@ -6401,7 +6541,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4200/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -6441,7 +6581,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X29" s="3"/>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>1.38%~1.42%</t>
+        </is>
+      </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6578,7 +6722,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C30" s="3"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>102684284.IB</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
           <t>5+N</t>
@@ -6617,7 +6765,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7650/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -6657,7 +6805,11 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X30" s="3"/>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>1.81%~1.91%</t>
+        </is>
+      </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6794,7 +6946,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C31" s="3"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>012682552.IB</t>
+        </is>
+      </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -6833,7 +6989,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4350/1.4200</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -6873,7 +7029,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X31" s="3"/>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>1.40%~1.44%</t>
+        </is>
+      </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -7006,7 +7166,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26南电MTN009(绿色科创债)</t>
+          <t>26南电GN009(科创债)</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7014,7 +7174,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C32" s="3"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>132680105.IB</t>
+        </is>
+      </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
           <t>4.99Y</t>
@@ -7053,7 +7217,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>1.6500/--</t>
+          <t>1.6200/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -7093,7 +7257,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X32" s="3"/>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>1.56%~1.66%</t>
+        </is>
+      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -7230,7 +7398,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C33" s="3"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>102684291.IB</t>
+        </is>
+      </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
           <t>1.04Y</t>
@@ -7269,7 +7441,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4100/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
@@ -7309,7 +7481,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X33" s="3"/>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>1.41%~1.51%</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -7446,7 +7622,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C34" s="3"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>102684292.IB</t>
+        </is>
+      </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -7517,7 +7697,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X34" s="3"/>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>1.66%~1.76%</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -7646,7 +7830,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26复星高科003(资产担保)</t>
+          <t>26复星高科CP003(资产担保)</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -7654,7 +7838,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C35" s="3"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>042680359.IB</t>
+        </is>
+      </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
           <t>1Y</t>
@@ -7733,7 +7921,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X35" s="3"/>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>3.54%~3.58%</t>
+        </is>
+      </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -7861,7 +8053,9 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AZ35" s="3"/>
+      <c r="AZ35" s="4" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
@@ -7874,7 +8068,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C36" s="3"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>102684279.IB</t>
+        </is>
+      </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -7913,7 +8111,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9100/1.8500</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -7953,7 +8151,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X36" s="3"/>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>1.79%~1.89%</t>
+        </is>
+      </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -8092,7 +8294,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C37" s="3"/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>102684290.IB</t>
+        </is>
+      </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -8131,7 +8337,7 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.9700</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
@@ -8171,7 +8377,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X37" s="3"/>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>1.83%~1.93%</t>
+        </is>
+      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -8335,19 +8545,27 @@
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>26恒泰MTN003</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>2.82Y</t>
+        </is>
+      </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.6241</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7300/1.6200</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -8383,7 +8601,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X38" s="3"/>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>1.49%~1.59%</t>
+        </is>
+      </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8555,7 +8777,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7225/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -8783,7 +9005,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5900/--</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -8823,7 +9045,11 @@
           <t>4-</t>
         </is>
       </c>
-      <c r="X40" s="3"/>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>1.59%~1.69%</t>
+        </is>
+      </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -9031,7 +9257,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X41" s="3"/>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>1.47%~1.57%</t>
+        </is>
+      </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -9251,7 +9481,11 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X42" s="3"/>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>2.74%~2.84%</t>
+        </is>
+      </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -9427,7 +9661,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>1.6600/--</t>
+          <t>1.6100/--</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -9467,7 +9701,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X43" s="3"/>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>1.60%~1.70%</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -9691,7 +9929,11 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X44" s="3"/>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>2.21%~2.31%</t>
+        </is>
+      </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -9911,7 +10153,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X45" s="3"/>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>1.75%~1.85%</t>
+        </is>
+      </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -10091,7 +10337,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>1.6100/--</t>
+          <t>--/1.6100</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -10131,7 +10377,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X46" s="3"/>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>1.64%~1.74%</t>
+        </is>
+      </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -10311,7 +10561,7 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7800</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
@@ -10351,7 +10601,11 @@
           <t>4-</t>
         </is>
       </c>
-      <c r="X47" s="3"/>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>1.71%~1.81%</t>
+        </is>
+      </c>
       <c r="Y47" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -10571,7 +10825,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X48" s="3"/>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>1.74%~1.84%</t>
+        </is>
+      </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -10791,7 +11049,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X49" s="3"/>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>1.68%~1.78%</t>
+        </is>
+      </c>
       <c r="Y49" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -11011,7 +11273,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="X50" s="3"/>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>1.68%~1.78%</t>
+        </is>
+      </c>
       <c r="Y50" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -11191,7 +11457,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7500</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
@@ -11231,7 +11497,11 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X51" s="3"/>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>1.78%~1.88%</t>
+        </is>
+      </c>
       <c r="Y51" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -11411,7 +11681,7 @@
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5800</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
@@ -11451,7 +11721,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X52" s="3"/>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>1.53%~1.63%</t>
+        </is>
+      </c>
       <c r="Y52" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -11627,7 +11901,7 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6900</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
@@ -11667,7 +11941,11 @@
           <t>4-</t>
         </is>
       </c>
-      <c r="X53" s="3"/>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>1.68%~1.78%</t>
+        </is>
+      </c>
       <c r="Y53" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -12035,7 +12313,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7500</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
@@ -12075,7 +12353,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X55" s="3"/>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>1.71%~1.81%</t>
+        </is>
+      </c>
       <c r="Y55" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -12283,7 +12565,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X56" s="3"/>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>1.85%~1.95%</t>
+        </is>
+      </c>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3" t="inlineStr">
@@ -12435,7 +12721,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>1.6000/--</t>
+          <t>1.6000/1.5400</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
@@ -12475,7 +12761,11 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X57" s="3"/>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>1.79%~1.89%</t>
+        </is>
+      </c>
       <c r="Y57" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -12699,7 +12989,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X58" s="3"/>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>1.63%~1.73%</t>
+        </is>
+      </c>
       <c r="Y58" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -13034,66 +13328,68 @@
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>26国元证券CP015</t>
+          <t>26龙城发展MTN005</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>10-27 17:00</t>
+          <t>10-27 18:00</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>072610208.IB</t>
+          <t>102684306.IB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>0.41Y</t>
+          <t>3+2+N</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="4" t="n">
-        <v>1.43</v>
-      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 1.90</t>
+        </is>
+      </c>
+      <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>26国元证券CP012</t>
+          <t>26龙城08</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>143D</t>
+          <t>4.72Y</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>1.4198</t>
+          <t>1.7364</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7200/--</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>国元证券股份有限公司</t>
+          <t>太原市龙城发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.29</t>
+          <t>C- 24.94</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -13103,7 +13399,7 @@
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>10-27 09:00</t>
+          <t>10-27 14:00</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr">
@@ -13125,7 +13421,7 @@
       </c>
       <c r="X60" s="3" t="inlineStr">
         <is>
-          <t>1.43%~1.47%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y60" s="3" t="inlineStr">
@@ -13136,19 +13432,23 @@
       <c r="Z60" s="3"/>
       <c r="AA60" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
-        </is>
-      </c>
-      <c r="AB60" s="3"/>
+          <t>山西省-太原市</t>
+        </is>
+      </c>
+      <c r="AB60" s="3" t="inlineStr">
+        <is>
+          <t>本期中期票据发行金额不超过5亿元，募集资金拟计划全部用于偿还公司债务融资工具本金，以进一步控制融资成本，提高直接融资比例，改善并优化公司整体的负债结构。[21龙城发展PPN003B,23龙城发展MTN006B]</t>
+        </is>
+      </c>
       <c r="AC60" s="3" t="inlineStr">
         <is>
-          <t>国元证券股份有限公司</t>
+          <t>兴业证券股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD60" s="3"/>
       <c r="AE60" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF60" s="3" t="inlineStr">
@@ -13163,7 +13463,7 @@
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>国元证券股份有限公司2026年度第十五期短期融资券</t>
+          <t>太原市龙城发展投资集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
@@ -13173,7 +13473,7 @@
       </c>
       <c r="AJ60" s="3" t="inlineStr">
         <is>
-          <t>2027-03-26</t>
+          <t>2031-10-28</t>
         </is>
       </c>
       <c r="AK60" s="3"/>
@@ -13194,32 +13494,32 @@
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP60" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ60" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT60" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU60" s="3" t="inlineStr">
@@ -13234,7 +13534,7 @@
       </c>
       <c r="AW60" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX60" s="3" t="inlineStr">
@@ -13252,64 +13552,66 @@
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26稠州银行小微债01</t>
+          <t>26国元证券CP015</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>10-27 18:00</t>
-        </is>
-      </c>
-      <c r="C61" s="3"/>
+          <t>10-27 17:00</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>072610208.IB</t>
+        </is>
+      </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.41Y</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
         <v>10.0</v>
       </c>
       <c r="F61" s="3"/>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>1.40 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="4" t="n">
+        <v>1.43</v>
+      </c>
       <c r="I61" s="3"/>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>24稠州商行小微债01</t>
+          <t>26国元证券CP012</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>335D</t>
+          <t>143D</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>1.4862</t>
+          <t>1.4198</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4500/--</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>浙江稠州商业银行股份有限公司</t>
+          <t>国元证券股份有限公司</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>A- 66.84</t>
+          <t>C+ 33.29</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -13329,55 +13631,47 @@
       </c>
       <c r="T61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="U61" s="3"/>
       <c r="V61" s="3"/>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X61" s="3" t="inlineStr">
         <is>
-          <t>1.81%~1.91%</t>
+          <t>1.43%~1.47%</t>
         </is>
       </c>
       <c r="Y61" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z61" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z61" s="3"/>
       <c r="AA61" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
-        </is>
-      </c>
-      <c r="AB61" s="3" t="inlineStr">
-        <is>
-          <t>本期债券发行的募集资金在扣除发行费用后,将依据适用法律和主管部门的批准全部用于发放小型微型企业贷款</t>
-        </is>
-      </c>
+          <t>安徽省-合肥市</t>
+        </is>
+      </c>
+      <c r="AB61" s="3"/>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,国泰海通证券股份有限公司</t>
+          <t>国元证券股份有限公司</t>
         </is>
       </c>
       <c r="AD61" s="3"/>
       <c r="AE61" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF61" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG61" s="3" t="inlineStr">
@@ -13387,7 +13681,7 @@
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>浙江稠州商业银行股份有限公司2026年小型微型企业贷款专项金融债券(第一期)</t>
+          <t>国元证券股份有限公司2026年度第十五期短期融资券</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
@@ -13397,23 +13691,23 @@
       </c>
       <c r="AJ61" s="3" t="inlineStr">
         <is>
-          <t>2029-10-29</t>
+          <t>2027-03-26</t>
         </is>
       </c>
       <c r="AK61" s="3"/>
       <c r="AL61" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AM61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AN61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AO61" s="3" t="inlineStr">
@@ -13423,27 +13717,27 @@
       </c>
       <c r="AP61" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ61" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT61" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU61" s="3" t="inlineStr">
@@ -13476,7 +13770,7 @@
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26浙能资本MTN002(科创债)</t>
+          <t>26稠州银行小微债01</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -13484,47 +13778,41 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>102684272.IB</t>
-        </is>
-      </c>
+      <c r="C62" s="3"/>
       <c r="D62" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F62" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F62" s="3"/>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>26动能03</t>
+          <t>24稠州商行小微债01</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>2.97Y+2.00Y</t>
+          <t>335D</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1.6433</t>
+          <t>1.4862</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -13534,10 +13822,14 @@
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>浙能资本控股有限公司</t>
-        </is>
-      </c>
-      <c r="P62" s="3"/>
+          <t>浙江稠州商业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>A- 66.84</t>
+        </is>
+      </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -13555,43 +13847,55 @@
       </c>
       <c r="T62" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="U62" s="3"/>
       <c r="V62" s="3"/>
-      <c r="W62" s="3"/>
-      <c r="X62" s="3"/>
+      <c r="W62" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>1.81%~1.91%</t>
+        </is>
+      </c>
       <c r="Y62" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z62" s="3"/>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z62" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行科技创新债券金额1亿元,拟全部用于置换一年以内自有资金出资及拟出资资金的基金出资款及偿还有息负债。</t>
+          <t>本期债券发行的募集资金在扣除发行费用后,将依据适用法律和主管部门的批准全部用于发放小型微型企业贷款</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,招商银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD62" s="3"/>
       <c r="AE62" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF62" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG62" s="3" t="inlineStr">
@@ -13601,7 +13905,7 @@
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>浙能资本控股有限公司2026年度第二期科技创新债券</t>
+          <t>浙江稠州商业银行股份有限公司2026年小型微型企业贷款专项金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
@@ -13611,53 +13915,53 @@
       </c>
       <c r="AJ62" s="3" t="inlineStr">
         <is>
-          <t>2029-10-28</t>
-        </is>
-      </c>
-      <c r="AK62" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-29</t>
+        </is>
+      </c>
+      <c r="AK62" s="3"/>
       <c r="AL62" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM62" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AN62" s="3" t="inlineStr">
+        <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="AM62" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="AN62" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
           <t>金融</t>
         </is>
       </c>
-      <c r="AP62" s="3"/>
+      <c r="AP62" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ62" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT62" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU62" s="3" t="inlineStr">
@@ -13690,7 +13994,7 @@
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>26赣水03</t>
+          <t>26浙能资本MTN002(科创债)</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -13700,60 +14004,58 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>525071.SZ</t>
+          <t>102684272.IB</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F63" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>1.25 ~ 2.25</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>26赣水01</t>
+          <t>26动能03</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>4.38Y</t>
+          <t>2.97Y+2.00Y</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>1.6574</t>
+          <t>1.6433</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6500/1.6400</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>江西省水利投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P63" s="3" t="inlineStr">
-        <is>
-          <t>C- 20.97</t>
-        </is>
-      </c>
+          <t>浙能资本控股有限公司</t>
+        </is>
+      </c>
+      <c r="P63" s="3"/>
       <c r="Q63" s="3" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -13761,7 +14063,7 @@
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t>10-27 16:00</t>
+          <t>10-27 09:00</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr">
@@ -13776,16 +14078,8 @@
       </c>
       <c r="U63" s="3"/>
       <c r="V63" s="3"/>
-      <c r="W63" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X63" s="3" t="inlineStr">
-        <is>
-          <t>1.61%~1.71%</t>
-        </is>
-      </c>
+      <c r="W63" s="3"/>
+      <c r="X63" s="3"/>
       <c r="Y63" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -13794,23 +14088,23 @@
       <c r="Z63" s="3"/>
       <c r="AA63" s="3" t="inlineStr">
         <is>
-          <t>江西省</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB63" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金10亿元,扣除发行费用后拟全部用于偿还有息负债</t>
+          <t>发行人本次发行科技创新债券金额1亿元,拟全部用于置换一年以内自有资金出资及拟出资资金的基金出资款及偿还有息负债。</t>
         </is>
       </c>
       <c r="AC63" s="3" t="inlineStr">
         <is>
-          <t>申万宏源证券有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,国盛证券股份有限公司,广发证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD63" s="3"/>
       <c r="AE63" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF63" s="3" t="inlineStr">
@@ -13820,12 +14114,12 @@
       </c>
       <c r="AG63" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH63" s="3" t="inlineStr">
         <is>
-          <t>江西省水利投资集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>浙能资本控股有限公司2026年度第二期科技创新债券</t>
         </is>
       </c>
       <c r="AI63" s="3" t="inlineStr">
@@ -13835,13 +14129,17 @@
       </c>
       <c r="AJ63" s="3" t="inlineStr">
         <is>
-          <t>2031-10-28</t>
-        </is>
-      </c>
-      <c r="AK63" s="3"/>
+          <t>2029-10-28</t>
+        </is>
+      </c>
+      <c r="AK63" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL63" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AM63" s="3" t="inlineStr">
@@ -13856,32 +14154,28 @@
       </c>
       <c r="AO63" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP63" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP63" s="3"/>
       <c r="AQ63" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT63" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU63" s="3" t="inlineStr">
@@ -13914,7 +14208,7 @@
     <row r="64" customHeight="true" ht="18.0">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>26浙创02</t>
+          <t>26赣水03</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -13924,58 +14218,58 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>246324.SH</t>
+          <t>525071.SZ</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.25 ~ 2.25</t>
         </is>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>24浙控K1</t>
+          <t>26赣水01</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>4.38Y</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>1.5241</t>
+          <t>1.6574</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6700/--</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>浙江省创新投资集团有限公司</t>
+          <t>江西省水利投资集团有限公司</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.20</t>
+          <t>C- 20.97</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -13985,7 +14279,7 @@
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>10-27 15:00</t>
+          <t>10-27 16:00</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr">
@@ -13995,19 +14289,19 @@
       </c>
       <c r="T64" s="3" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="U64" s="3"/>
       <c r="V64" s="3"/>
       <c r="W64" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.63%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
@@ -14018,17 +14312,17 @@
       <c r="Z64" s="3"/>
       <c r="AA64" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>江西省</t>
         </is>
       </c>
       <c r="AB64" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金规模不超过12.00亿元(含12.00亿元),扣除发行费用后拟全部用于偿还到期的公司债券本金[23浙金03]</t>
+          <t>本期债券募集资金10亿元,扣除发行费用后拟全部用于偿还有息负债</t>
         </is>
       </c>
       <c r="AC64" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中信建投证券股份有限公司,财通证券股份有限公司</t>
+          <t>申万宏源证券有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,国盛证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD64" s="3"/>
@@ -14044,12 +14338,12 @@
       </c>
       <c r="AG64" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH64" s="3" t="inlineStr">
         <is>
-          <t>浙江省创新投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>江西省水利投资集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI64" s="3" t="inlineStr">
@@ -14059,7 +14353,7 @@
       </c>
       <c r="AJ64" s="3" t="inlineStr">
         <is>
-          <t>2029-11-02</t>
+          <t>2031-10-28</t>
         </is>
       </c>
       <c r="AK64" s="3"/>
@@ -14075,37 +14369,37 @@
       </c>
       <c r="AN64" s="3" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP64" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ64" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT64" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU64" s="3" t="inlineStr">
@@ -14138,7 +14432,7 @@
     <row r="65" customHeight="true" ht="18.0">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>26鲁信投资MTN001(科创债)</t>
+          <t>26浙创02</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -14146,41 +14440,45 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C65" s="3"/>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>246324.SH</t>
+        </is>
+      </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.40</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>25鲁信投资MTN001(科创债)</t>
+          <t>24浙控K1</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>3.54Y</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>1.8657</t>
+          <t>1.5241</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
@@ -14190,12 +14488,12 @@
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>鲁信创业投资集团股份有限公司</t>
+          <t>浙江省创新投资集团有限公司</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>C 29.14</t>
+          <t>C+ 34.20</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -14205,7 +14503,7 @@
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>10-27 14:00</t>
+          <t>10-27 15:00</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr">
@@ -14215,42 +14513,46 @@
       </c>
       <c r="T65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
       <c r="W65" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X65" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X65" s="3" t="inlineStr">
+        <is>
+          <t>1.53%~1.63%</t>
+        </is>
+      </c>
       <c r="Y65" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z65" s="3"/>
       <c r="AA65" s="3" t="inlineStr">
         <is>
-          <t>山东省-淄博市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB65" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具募集资金中50,000.00万元拟通过直接投资,或设立契约型基金、公司型基金,以及设立有限合伙企业等方式投资科技创新企业公司的股权或置换发行人对上述科技创新领域相关投资</t>
+          <t>本期债券募集资金规模不超过12.00亿元(含12.00亿元),扣除发行费用后拟全部用于偿还到期的公司债券本金[23浙金03]</t>
         </is>
       </c>
       <c r="AC65" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,青岛银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中信建投证券股份有限公司,财通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD65" s="3"/>
       <c r="AE65" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF65" s="3" t="inlineStr">
@@ -14260,12 +14562,12 @@
       </c>
       <c r="AG65" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH65" s="3" t="inlineStr">
         <is>
-          <t>鲁信创业投资集团股份有限公司2026年度第一期科技创新债券</t>
+          <t>浙江省创新投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI65" s="3" t="inlineStr">
@@ -14275,23 +14577,23 @@
       </c>
       <c r="AJ65" s="3" t="inlineStr">
         <is>
-          <t>2031-10-28</t>
+          <t>2029-11-02</t>
         </is>
       </c>
       <c r="AK65" s="3"/>
       <c r="AL65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t/>
         </is>
       </c>
       <c r="AM65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AN65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="AO65" s="3" t="inlineStr">
@@ -14301,7 +14603,7 @@
       </c>
       <c r="AP65" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ65" s="3" t="inlineStr">
@@ -14311,17 +14613,17 @@
       </c>
       <c r="AR65" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS65" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT65" s="3" t="inlineStr">
         <is>
-          <t>通用机械</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU65" s="3" t="inlineStr">
@@ -14354,7 +14656,7 @@
     <row r="66" customHeight="true" ht="18.0">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>26扬州经开MTN001</t>
+          <t>26鲁信投资MTN001(科创债)</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -14362,41 +14664,45 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C66" s="3"/>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>102690088.IB</t>
+        </is>
+      </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>2.5</v>
+        <v>5.0</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.70 ~ 2.40</t>
         </is>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>26扬开05</t>
+          <t>25鲁信投资MTN001(科创债)</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>4.79Y</t>
+          <t>3.54Y</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>1.8117</t>
+          <t>1.8657</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
@@ -14406,12 +14712,12 @@
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>扬州经济技术开发区开发(集团)有限公司</t>
+          <t>鲁信创业投资集团股份有限公司</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>C- 24.69</t>
+          <t>C 29.14</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -14421,7 +14727,7 @@
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>10-27 09:00</t>
+          <t>10-27 14:00</t>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr">
@@ -14438,29 +14744,33 @@
       <c r="V66" s="3"/>
       <c r="W66" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X66" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X66" s="3" t="inlineStr">
+        <is>
+          <t>1.84%~1.94%</t>
+        </is>
+      </c>
       <c r="Y66" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z66" s="3"/>
       <c r="AA66" s="3" t="inlineStr">
         <is>
-          <t>江苏省-扬州市</t>
+          <t>山东省-淄博市</t>
         </is>
       </c>
       <c r="AB66" s="3" t="inlineStr">
         <is>
-          <t>本期拟发行中期票据2.50亿元,募集资金用于偿还债务融资工具本金[21扬州经开MTN002B]</t>
+          <t>本期债务融资工具募集资金中50,000.00万元拟通过直接投资,或设立契约型基金、公司型基金,以及设立有限合伙企业等方式投资科技创新企业公司的股权或置换发行人对上述科技创新领域相关投资</t>
         </is>
       </c>
       <c r="AC66" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
+          <t>中信证券股份有限公司,青岛银行股份有限公司</t>
         </is>
       </c>
       <c r="AD66" s="3"/>
@@ -14481,7 +14791,7 @@
       </c>
       <c r="AH66" s="3" t="inlineStr">
         <is>
-          <t>扬州经济技术开发区开发(集团)有限公司2026年度第一期中期票据</t>
+          <t>鲁信创业投资集团股份有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI66" s="3" t="inlineStr">
@@ -14512,7 +14822,7 @@
       </c>
       <c r="AO66" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP66" s="3" t="inlineStr">
@@ -14522,22 +14832,22 @@
       </c>
       <c r="AQ66" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR66" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS66" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT66" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>通用机械</t>
         </is>
       </c>
       <c r="AU66" s="3" t="inlineStr">
@@ -14552,7 +14862,7 @@
       </c>
       <c r="AW66" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX66" s="3" t="inlineStr">
@@ -14565,12 +14875,14 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AZ66" s="3"/>
+      <c r="AZ66" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="67" customHeight="true" ht="18.0">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>26桐昆控股SCP013</t>
+          <t>26扬州经开MTN001</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -14578,56 +14890,60 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C67" s="3"/>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>102684274.IB</t>
+        </is>
+      </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>0.73Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>3.0</v>
+        <v>2.5</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.49</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>25桐昆控股MTN001</t>
+          <t>26扬开05</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>235D</t>
+          <t>4.79Y</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>1.4787</t>
+          <t>1.8117</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8500/1.8000</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>桐昆控股集团有限公司</t>
+          <t>扬州经济技术开发区开发(集团)有限公司</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>C- 11.83</t>
+          <t>C- 24.69</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -14654,10 +14970,14 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X67" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X67" s="3" t="inlineStr">
+        <is>
+          <t>1.74%~1.84%</t>
+        </is>
+      </c>
       <c r="Y67" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -14666,28 +14986,28 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>江苏省-扬州市</t>
         </is>
       </c>
       <c r="AB67" s="3" t="inlineStr">
         <is>
-          <t>发行人本次超短期融资券发行3亿元(本期承销费从募集资金中扣除),用于偿还即将到期的债务融资工具。[26桐昆控股SCP002(科创债)]</t>
+          <t>本期拟发行中期票据2.50亿元,募集资金用于偿还债务融资工具本金[21扬州经开MTN002B]</t>
         </is>
       </c>
       <c r="AC67" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF67" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG67" s="3" t="inlineStr">
@@ -14697,7 +15017,7 @@
       </c>
       <c r="AH67" s="3" t="inlineStr">
         <is>
-          <t>桐昆控股集团有限公司2026年度第十三期超短期融资券</t>
+          <t>扬州经济技术开发区开发(集团)有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI67" s="3" t="inlineStr">
@@ -14707,7 +15027,7 @@
       </c>
       <c r="AJ67" s="3" t="inlineStr">
         <is>
-          <t>2027-07-23</t>
+          <t>2031-10-28</t>
         </is>
       </c>
       <c r="AK67" s="3"/>
@@ -14728,32 +15048,32 @@
       </c>
       <c r="AO67" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP67" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ67" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR67" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS67" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT67" s="3" t="inlineStr">
         <is>
-          <t>化学纤维</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU67" s="3" t="inlineStr">
@@ -14768,7 +15088,7 @@
       </c>
       <c r="AW67" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX67" s="3" t="inlineStr">
@@ -14781,12 +15101,14 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AZ67" s="3"/>
+      <c r="AZ67" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="68" customHeight="true" ht="18.0">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>26绿原国资MTN001</t>
+          <t>26桐昆控股SCP013</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -14794,10 +15116,14 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C68" s="3"/>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>012682553.IB</t>
+        </is>
+      </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.73Y</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
@@ -14806,21 +15132,29 @@
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.40 ~ 1.49</t>
         </is>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K68" s="3"/>
-      <c r="L68" s="3"/>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>25桐昆控股MTN001</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>235D</t>
+        </is>
+      </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.4787</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
@@ -14830,12 +15164,12 @@
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>新疆绿原国有资本投资运营有限公司</t>
+          <t>桐昆控股集团有限公司</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C- 11.83</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -14845,7 +15179,7 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>10-27 15:00</t>
+          <t>10-27 09:00</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr">
@@ -14862,40 +15196,44 @@
       <c r="V68" s="3"/>
       <c r="W68" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X68" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X68" s="3" t="inlineStr">
+        <is>
+          <t>1.47%~1.51%</t>
+        </is>
+      </c>
       <c r="Y68" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z68" s="3"/>
       <c r="AA68" s="3" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区-铁门关市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB68" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0亿元,发行规模为上限为3亿元,用于偿还有息债务本息。</t>
+          <t>发行人本次超短期融资券发行3亿元(本期承销费从募集资金中扣除),用于偿还即将到期的债务融资工具。[26桐昆控股SCP002(科创债)]</t>
         </is>
       </c>
       <c r="AC68" s="3" t="inlineStr">
         <is>
-          <t>申万宏源证券有限公司</t>
+          <t>浙商银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD68" s="3"/>
       <c r="AE68" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF68" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG68" s="3" t="inlineStr">
@@ -14905,7 +15243,7 @@
       </c>
       <c r="AH68" s="3" t="inlineStr">
         <is>
-          <t>新疆绿原国有资本投资运营有限公司2026年度第一期中期票据</t>
+          <t>桐昆控股集团有限公司2026年度第十三期超短期融资券</t>
         </is>
       </c>
       <c r="AI68" s="3" t="inlineStr">
@@ -14915,14 +15253,10 @@
       </c>
       <c r="AJ68" s="3" t="inlineStr">
         <is>
-          <t>2029-10-28</t>
-        </is>
-      </c>
-      <c r="AK68" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-07-23</t>
+        </is>
+      </c>
+      <c r="AK68" s="3"/>
       <c r="AL68" s="3" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -14940,32 +15274,32 @@
       </c>
       <c r="AO68" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP68" s="3" t="inlineStr">
         <is>
-          <t>7.5*无效</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ68" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR68" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AS68" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AT68" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化学纤维</t>
         </is>
       </c>
       <c r="AU68" s="3" t="inlineStr">
@@ -14998,7 +15332,7 @@
     <row r="69" customHeight="true" ht="18.0">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>26南航股MTN003</t>
+          <t>26绿原国资MTN001</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -15006,41 +15340,37 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C69" s="3"/>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>102684287.IB</t>
+        </is>
+      </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>34.0</v>
+        <v>3.0</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>1.41 ~ 1.71</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>24南航股MTN012</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
-        <is>
-          <t>2.99Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3"/>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>1.5741</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
@@ -15050,12 +15380,12 @@
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>中国南方航空股份有限公司</t>
+          <t>新疆绿原国有资本投资运营有限公司</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>B- 38.31</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -15065,7 +15395,7 @@
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t>10-27 09:00</t>
+          <t>10-27 15:00</t>
         </is>
       </c>
       <c r="S69" s="3" t="inlineStr">
@@ -15082,29 +15412,33 @@
       <c r="V69" s="3"/>
       <c r="W69" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X69" s="3"/>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X69" s="3" t="inlineStr">
+        <is>
+          <t>2.15%~2.25%</t>
+        </is>
+      </c>
       <c r="Y69" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z69" s="3"/>
       <c r="AA69" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>新疆维吾尔自治区-铁门关市</t>
         </is>
       </c>
       <c r="AB69" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额为34亿元，发行人计划用于偿还存量有息债务</t>
+          <t>本期中期票据基础发行规模为0亿元,发行规模为上限为3亿元,用于偿还有息债务本息。</t>
         </is>
       </c>
       <c r="AC69" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国农业银行股份有限公司</t>
+          <t>申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD69" s="3"/>
@@ -15115,7 +15449,7 @@
       </c>
       <c r="AF69" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG69" s="3" t="inlineStr">
@@ -15125,7 +15459,7 @@
       </c>
       <c r="AH69" s="3" t="inlineStr">
         <is>
-          <t>中国南方航空股份有限公司2026年度第三期中期票据</t>
+          <t>新疆绿原国有资本投资运营有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI69" s="3" t="inlineStr">
@@ -15160,32 +15494,32 @@
       </c>
       <c r="AO69" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP69" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7.5*无效</t>
         </is>
       </c>
       <c r="AQ69" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR69" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS69" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT69" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU69" s="3" t="inlineStr">
@@ -15218,7 +15552,7 @@
     <row r="70" customHeight="true" ht="18.0">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>26鲁金MTN002A</t>
+          <t>26南航股MTN003</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -15226,56 +15560,60 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C70" s="3"/>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>102684293.IB</t>
+        </is>
+      </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>12.0</v>
+        <v>34.0</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.41 ~ 1.71</t>
         </is>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>24鲁金K1</t>
+          <t>24南航股MTN012</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>2.41Y</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>1.4767</t>
+          <t>1.5741</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5900/--</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>山东黄金矿业股份有限公司</t>
+          <t>中国南方航空股份有限公司</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>B+ 56.67</t>
+          <t>B- 38.31</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -15302,33 +15640,33 @@
       <c r="V70" s="3"/>
       <c r="W70" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X70" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X70" s="3" t="inlineStr">
+        <is>
+          <t>1.54%~1.64%</t>
+        </is>
+      </c>
       <c r="Y70" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z70" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z70" s="3"/>
       <c r="AA70" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB70" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模上限25亿元,募集资金用于偿还发行人存续有息负债。</t>
+          <t>本期债务融资工具发行金额为34亿元，发行人计划用于偿还存量有息债务</t>
         </is>
       </c>
       <c r="AC70" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,广发证券股份有限公司</t>
+          <t>兴业银行股份有限公司,中国农业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD70" s="3"/>
@@ -15339,7 +15677,7 @@
       </c>
       <c r="AF70" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG70" s="3" t="inlineStr">
@@ -15349,7 +15687,7 @@
       </c>
       <c r="AH70" s="3" t="inlineStr">
         <is>
-          <t>山东黄金矿业股份有限公司2026年度第二期中期票据(品种一)</t>
+          <t>中国南方航空股份有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI70" s="3" t="inlineStr">
@@ -15359,10 +15697,14 @@
       </c>
       <c r="AJ70" s="3" t="inlineStr">
         <is>
-          <t>2031-10-28</t>
-        </is>
-      </c>
-      <c r="AK70" s="3"/>
+          <t>2029-10-28</t>
+        </is>
+      </c>
+      <c r="AK70" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL70" s="3" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -15385,27 +15727,27 @@
       </c>
       <c r="AP70" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ70" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR70" s="3" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AS70" s="3" t="inlineStr">
         <is>
-          <t>贵金属</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AT70" s="3" t="inlineStr">
         <is>
-          <t>黄金</t>
+          <t>航空运输</t>
         </is>
       </c>
       <c r="AU70" s="3" t="inlineStr">
@@ -15433,12 +15775,14 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AZ70" s="3"/>
+      <c r="AZ70" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="71" customHeight="true" ht="18.0">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>26高淳经开MTN006</t>
+          <t>26鲁金MTN002A</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -15446,56 +15790,60 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C71" s="3"/>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>102684299.IB</t>
+        </is>
+      </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>2.97</v>
+        <v>12.0</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>26高淳经开MTN005</t>
+          <t>24鲁金K1</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>2.41Y</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>1.6383</t>
+          <t>1.4767</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4900/--</t>
         </is>
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>江苏高淳经济开发区开发集团有限公司</t>
+          <t>山东黄金矿业股份有限公司</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>C- 19.11</t>
+          <t>B+ 56.67</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -15522,29 +15870,37 @@
       <c r="V71" s="3"/>
       <c r="W71" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
-        </is>
-      </c>
-      <c r="X71" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X71" s="3" t="inlineStr">
+        <is>
+          <t>1.63%~1.73%</t>
+        </is>
+      </c>
       <c r="Y71" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z71" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z71" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA71" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB71" s="3" t="inlineStr">
         <is>
-          <t>本次债务融资工具发行金额2.97亿元,所募集资金拟用于偿还发行人即将到期债务融资工具本金。[25高淳经开PPN002]</t>
+          <t>本期中期票据发行规模上限25亿元,募集资金用于偿还发行人存续有息负债。</t>
         </is>
       </c>
       <c r="AC71" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,浙商证券股份有限公司</t>
+          <t>招商银行股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD71" s="3"/>
@@ -15565,7 +15921,7 @@
       </c>
       <c r="AH71" s="3" t="inlineStr">
         <is>
-          <t>江苏高淳经济开发区开发集团有限公司2026年度第六期中期票据</t>
+          <t>山东黄金矿业股份有限公司2026年度第二期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI71" s="3" t="inlineStr">
@@ -15575,14 +15931,10 @@
       </c>
       <c r="AJ71" s="3" t="inlineStr">
         <is>
-          <t>2029-10-28</t>
-        </is>
-      </c>
-      <c r="AK71" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-28</t>
+        </is>
+      </c>
+      <c r="AK71" s="3"/>
       <c r="AL71" s="3" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -15600,32 +15952,32 @@
       </c>
       <c r="AO71" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP71" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ71" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR71" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="AS71" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>贵金属</t>
         </is>
       </c>
       <c r="AT71" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>黄金</t>
         </is>
       </c>
       <c r="AU71" s="3" t="inlineStr">
@@ -15658,7 +16010,7 @@
     <row r="72" customHeight="true" ht="18.0">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>26凤城河MTN008</t>
+          <t>26高淳经开MTN006</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -15666,56 +16018,60 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C72" s="3"/>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>102684296.IB</t>
+        </is>
+      </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>5.0</v>
+        <v>2.97</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.10</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>26凤城河MTN007</t>
+          <t>26高淳经开MTN005</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>1.6387</t>
+          <t>1.6383</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8000/1.6300</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>泰州凤城河建设发展有限公司</t>
+          <t>江苏高淳经济开发区开发集团有限公司</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>C 26.75</t>
+          <t>C- 19.11</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -15742,10 +16098,14 @@
       <c r="V72" s="3"/>
       <c r="W72" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X72" s="3"/>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X72" s="3" t="inlineStr">
+        <is>
+          <t>1.60%~1.70%</t>
+        </is>
+      </c>
       <c r="Y72" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -15754,17 +16114,17 @@
       <c r="Z72" s="3"/>
       <c r="AA72" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB72" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行金额为5亿元,用于偿还发行人存量债务融资工具本金[25凤城河CP004]</t>
+          <t>本次债务融资工具发行金额2.97亿元,所募集资金拟用于偿还发行人即将到期债务融资工具本金。[25高淳经开PPN002]</t>
         </is>
       </c>
       <c r="AC72" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>中信银行股份有限公司,浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD72" s="3"/>
@@ -15785,7 +16145,7 @@
       </c>
       <c r="AH72" s="3" t="inlineStr">
         <is>
-          <t>泰州凤城河建设发展有限公司2026年度第八期中期票据</t>
+          <t>江苏高淳经济开发区开发集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI72" s="3" t="inlineStr">
@@ -15820,7 +16180,7 @@
       </c>
       <c r="AO72" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP72" s="3" t="inlineStr">
@@ -15835,12 +16195,12 @@
       </c>
       <c r="AR72" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS72" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT72" s="3" t="inlineStr">
@@ -15878,7 +16238,7 @@
     <row r="73" customHeight="true" ht="18.0">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>26十堰国投MTN001</t>
+          <t>26凤城河MTN008</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -15886,56 +16246,60 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C73" s="3"/>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>102684276.IB</t>
+        </is>
+      </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>4.14</v>
+        <v>5.0</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.40 ~ 2.10</t>
         </is>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>25十堰国投MTN001</t>
+          <t>26凤城河MTN007</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>1.83Y</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>1.6924</t>
+          <t>1.6387</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>1.7200/--</t>
+          <t>1.6600/1.6300</t>
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>十堰国有资本投资运营集团有限公司</t>
+          <t>泰州凤城河建设发展有限公司</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>C 28.35</t>
+          <t>C 26.75</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -15945,7 +16309,7 @@
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>10-27 10:00</t>
+          <t>10-27 09:00</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr">
@@ -15962,29 +16326,33 @@
       <c r="V73" s="3"/>
       <c r="W73" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X73" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X73" s="3" t="inlineStr">
+        <is>
+          <t>1.58%~1.68%</t>
+        </is>
+      </c>
       <c r="Y73" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z73" s="3"/>
       <c r="AA73" s="3" t="inlineStr">
         <is>
-          <t>湖北省-十堰市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB73" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行金额为0亿元,发行金额上限为4.14亿元,募集资金将用于偿还发行人存量债务融资工具本金[21十堰国投PPN003,21十堰国投PPN004]</t>
+          <t>本次中期票据发行金额为5亿元,用于偿还发行人存量债务融资工具本金[25凤城河CP004]</t>
         </is>
       </c>
       <c r="AC73" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,广发银行股份有限公司</t>
+          <t>中信银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD73" s="3"/>
@@ -16005,7 +16373,7 @@
       </c>
       <c r="AH73" s="3" t="inlineStr">
         <is>
-          <t>十堰国有资本投资运营集团有限公司2026年度第一期中期票据</t>
+          <t>泰州凤城河建设发展有限公司2026年度第八期中期票据</t>
         </is>
       </c>
       <c r="AI73" s="3" t="inlineStr">
@@ -16015,10 +16383,14 @@
       </c>
       <c r="AJ73" s="3" t="inlineStr">
         <is>
-          <t>2031-10-28</t>
-        </is>
-      </c>
-      <c r="AK73" s="3"/>
+          <t>2029-10-28</t>
+        </is>
+      </c>
+      <c r="AK73" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL73" s="3" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -16036,7 +16408,7 @@
       </c>
       <c r="AO73" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP73" s="3" t="inlineStr">
@@ -16051,12 +16423,12 @@
       </c>
       <c r="AR73" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS73" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT73" s="3" t="inlineStr">
@@ -16094,7 +16466,7 @@
     <row r="74" customHeight="true" ht="18.0">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>26西安高新MTN012</t>
+          <t>26十堰国投MTN001</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -16102,14 +16474,18 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C74" s="3"/>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>102684282.IB</t>
+        </is>
+      </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>10.0</v>
+        <v>4.14</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="inlineStr">
@@ -16121,37 +16497,37 @@
       <c r="I74" s="3"/>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>26西安高新MTN010</t>
+          <t>25十堰国投MTN001</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>1.83Y</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>2.0170</t>
+          <t>1.6924</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7200/--</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>西安高新控股有限公司</t>
+          <t>十堰国有资本投资运营集团有限公司</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.72</t>
+          <t>C 28.35</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -16161,7 +16537,7 @@
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>10-27 09:00</t>
+          <t>10-27 10:00</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr">
@@ -16181,26 +16557,30 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X74" s="3"/>
+      <c r="X74" s="3" t="inlineStr">
+        <is>
+          <t>1.66%~1.76%</t>
+        </is>
+      </c>
       <c r="Y74" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z74" s="3"/>
       <c r="AA74" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>湖北省-十堰市</t>
         </is>
       </c>
       <c r="AB74" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行金额人民币0亿元,发行金额上限人民币10亿元,募集资金全部拟用于偿还发行人到期债务[25西安高新CP014,26西安高新CP001,24西安高新MTN001]</t>
+          <t>本期中期票据基础发行金额为0亿元,发行金额上限为4.14亿元,募集资金将用于偿还发行人存量债务融资工具本金[21十堰国投PPN003,21十堰国投PPN004]</t>
         </is>
       </c>
       <c r="AC74" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,渤海银行股份有限公司</t>
+          <t>长江证券股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD74" s="3"/>
@@ -16221,7 +16601,7 @@
       </c>
       <c r="AH74" s="3" t="inlineStr">
         <is>
-          <t>西安高新控股有限公司2026年度第十二期中期票据</t>
+          <t>十堰国有资本投资运营集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI74" s="3" t="inlineStr">
@@ -16231,14 +16611,10 @@
       </c>
       <c r="AJ74" s="3" t="inlineStr">
         <is>
-          <t>2029-10-28</t>
-        </is>
-      </c>
-      <c r="AK74" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-28</t>
+        </is>
+      </c>
+      <c r="AK74" s="3"/>
       <c r="AL74" s="3" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -16256,12 +16632,12 @@
       </c>
       <c r="AO74" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP74" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ74" s="3" t="inlineStr">
@@ -16271,12 +16647,12 @@
       </c>
       <c r="AR74" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS74" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT74" s="3" t="inlineStr">
@@ -16309,12 +16685,14 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AZ74" s="3"/>
+      <c r="AZ74" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="75" customHeight="true" ht="18.0">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>26龙城发展MTN005</t>
+          <t>26西安高新MTN012</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -16322,56 +16700,60 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C75" s="3"/>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>102684304.IB</t>
+        </is>
+      </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>26龙城08</t>
+          <t>26西安高新MTN010</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>4.72Y</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>1.7364</t>
+          <t>2.0170</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.0100</t>
         </is>
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>太原市龙城发展投资集团有限公司</t>
+          <t>西安高新控股有限公司</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>C- 24.94</t>
+          <t>C+ 32.72</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -16381,7 +16763,7 @@
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>10-27 14:00</t>
+          <t>10-27 09:00</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr">
@@ -16398,10 +16780,14 @@
       <c r="V75" s="3"/>
       <c r="W75" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X75" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X75" s="3" t="inlineStr">
+        <is>
+          <t>1.91%~2.01%</t>
+        </is>
+      </c>
       <c r="Y75" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -16410,17 +16796,17 @@
       <c r="Z75" s="3"/>
       <c r="AA75" s="3" t="inlineStr">
         <is>
-          <t>山西省-太原市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB75" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额不超过5亿元，募集资金拟计划全部用于偿还公司债务融资工具本金，以进一步控制融资成本，提高直接融资比例，改善并优化公司整体的负债结构。[21龙城发展PPN003B,23龙城发展MTN006B]</t>
+          <t>发行人本期中期票据基础发行金额人民币0亿元,发行金额上限人民币10亿元,募集资金全部拟用于偿还发行人到期债务[25西安高新CP014,26西安高新CP001,24西安高新MTN001]</t>
         </is>
       </c>
       <c r="AC75" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司,中国银行股份有限公司</t>
+          <t>中信银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD75" s="3"/>
@@ -16441,7 +16827,7 @@
       </c>
       <c r="AH75" s="3" t="inlineStr">
         <is>
-          <t>太原市龙城发展投资集团有限公司2026年度第五期中期票据</t>
+          <t>西安高新控股有限公司2026年度第十二期中期票据</t>
         </is>
       </c>
       <c r="AI75" s="3" t="inlineStr">
@@ -16451,10 +16837,14 @@
       </c>
       <c r="AJ75" s="3" t="inlineStr">
         <is>
-          <t>2031-10-28</t>
-        </is>
-      </c>
-      <c r="AK75" s="3"/>
+          <t>2029-10-28</t>
+        </is>
+      </c>
+      <c r="AK75" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL75" s="3" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -16472,27 +16862,27 @@
       </c>
       <c r="AO75" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP75" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ75" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR75" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS75" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT75" s="3" t="inlineStr">
@@ -16512,7 +16902,7 @@
       </c>
       <c r="AW75" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX75" s="3" t="inlineStr">
@@ -16525,7 +16915,9 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AZ75" s="3"/>
+      <c r="AZ75" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="76" customHeight="true" ht="18.0">
       <c r="A76" s="3" t="inlineStr">
@@ -16538,7 +16930,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C76" s="3"/>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>102684288.IB</t>
+        </is>
+      </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -16617,7 +17013,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X76" s="3"/>
+      <c r="X76" s="3" t="inlineStr">
+        <is>
+          <t>2.15%~2.25%</t>
+        </is>
+      </c>
       <c r="Y76" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -16749,7 +17149,9 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AZ76" s="3"/>
+      <c r="AZ76" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="77" customHeight="true" ht="18.0">
       <c r="A77" s="3" t="inlineStr">
@@ -16762,7 +17164,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C77" s="3"/>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>102684294.IB</t>
+        </is>
+      </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -16841,7 +17247,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X77" s="3"/>
+      <c r="X77" s="3" t="inlineStr">
+        <is>
+          <t>1.62%~1.72%</t>
+        </is>
+      </c>
       <c r="Y77" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -16965,7 +17375,9 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AZ77" s="3"/>
+      <c r="AZ77" s="4" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="78" customHeight="true" ht="18.0">
       <c r="A78" s="3" t="inlineStr">
@@ -16978,7 +17390,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C78" s="3"/>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>102690084.IB</t>
+        </is>
+      </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
           <t>3+N</t>
@@ -17017,7 +17433,7 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6000/1.5700</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
@@ -17057,7 +17473,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="X78" s="3"/>
+      <c r="X78" s="3" t="inlineStr">
+        <is>
+          <t>1.63%~1.73%</t>
+        </is>
+      </c>
       <c r="Y78" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -17198,7 +17618,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C79" s="3"/>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>012682551.IB</t>
+        </is>
+      </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -17277,7 +17701,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X79" s="3"/>
+      <c r="X79" s="3" t="inlineStr">
+        <is>
+          <t>1.47%~1.51%</t>
+        </is>
+      </c>
       <c r="Y79" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -17418,7 +17846,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C80" s="3"/>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>102684300.IB</t>
+        </is>
+      </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
           <t>15Y</t>
@@ -17457,7 +17889,7 @@
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9600/1.9500</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
@@ -17497,7 +17929,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X80" s="3"/>
+      <c r="X80" s="3" t="inlineStr">
+        <is>
+          <t>2.04%~2.14%</t>
+        </is>
+      </c>
       <c r="Y80" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -17638,7 +18074,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C81" s="3"/>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>102684297.IB</t>
+        </is>
+      </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -17717,7 +18157,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X81" s="3"/>
+      <c r="X81" s="3" t="inlineStr">
+        <is>
+          <t>1.71%~1.81%</t>
+        </is>
+      </c>
       <c r="Y81" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -17860,7 +18304,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C82" s="3"/>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>102684298.IB</t>
+        </is>
+      </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -17899,7 +18347,7 @@
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7900/1.7700</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
@@ -17939,7 +18387,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X82" s="3"/>
+      <c r="X82" s="3" t="inlineStr">
+        <is>
+          <t>1.69%~1.79%</t>
+        </is>
+      </c>
       <c r="Y82" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -18067,7 +18519,9 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AZ82" s="3"/>
+      <c r="AZ82" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="83" customHeight="true" ht="18.0">
       <c r="A83" s="3" t="inlineStr">
@@ -18080,7 +18534,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C83" s="3"/>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>102684283.IB</t>
+        </is>
+      </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -18119,7 +18577,7 @@
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6300/--</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
@@ -18159,7 +18617,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X83" s="3"/>
+      <c r="X83" s="3" t="inlineStr">
+        <is>
+          <t>1.65%~1.75%</t>
+        </is>
+      </c>
       <c r="Y83" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -18300,7 +18762,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C84" s="3"/>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>102684302.IB</t>
+        </is>
+      </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -18339,7 +18805,7 @@
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8200/1.7100</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
@@ -18379,7 +18845,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X84" s="3"/>
+      <c r="X84" s="3" t="inlineStr">
+        <is>
+          <t>1.70%~1.80%</t>
+        </is>
+      </c>
       <c r="Y84" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -18503,7 +18973,9 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AZ84" s="3"/>
+      <c r="AZ84" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="85" customHeight="true" ht="18.0">
       <c r="A85" s="3" t="inlineStr">
@@ -18516,7 +18988,11 @@
           <t>10-27 18:00</t>
         </is>
       </c>
-      <c r="C85" s="3"/>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>102684305.IB</t>
+        </is>
+      </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
           <t>2Y</t>
@@ -18555,7 +19031,7 @@
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5900/--</t>
         </is>
       </c>
       <c r="O85" s="3" t="inlineStr">
@@ -18595,7 +19071,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X85" s="3"/>
+      <c r="X85" s="3" t="inlineStr">
+        <is>
+          <t>1.52%~1.62%</t>
+        </is>
+      </c>
       <c r="Y85" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -18723,7 +19203,9 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AZ85" s="3"/>
+      <c r="AZ85" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="86" customHeight="true" ht="18.0">
       <c r="A86" s="3" t="inlineStr">
@@ -18779,7 +19261,7 @@
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7550/1.7450</t>
         </is>
       </c>
       <c r="O86" s="3" t="inlineStr">
@@ -18819,7 +19301,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X86" s="3"/>
+      <c r="X86" s="3" t="inlineStr">
+        <is>
+          <t>1.69%~1.79%</t>
+        </is>
+      </c>
       <c r="Y86" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -18999,7 +19485,7 @@
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O87" s="3" t="inlineStr">
@@ -19039,7 +19525,11 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X87" s="3"/>
+      <c r="X87" s="3" t="inlineStr">
+        <is>
+          <t>1.75%~1.85%</t>
+        </is>
+      </c>
       <c r="Y87" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -19227,7 +19717,7 @@
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8800</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr">
@@ -19267,7 +19757,11 @@
           <t>7-</t>
         </is>
       </c>
-      <c r="X88" s="3"/>
+      <c r="X88" s="3" t="inlineStr">
+        <is>
+          <t>2.03%~2.13%</t>
+        </is>
+      </c>
       <c r="Y88" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -19451,7 +19945,7 @@
       </c>
       <c r="N89" s="3" t="inlineStr">
         <is>
-          <t>1.7700/--</t>
+          <t>1.7700/1.6500</t>
         </is>
       </c>
       <c r="O89" s="3" t="inlineStr">
@@ -19491,7 +19985,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X89" s="3"/>
+      <c r="X89" s="3" t="inlineStr">
+        <is>
+          <t>1.65%~1.75%</t>
+        </is>
+      </c>
       <c r="Y89" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -19671,7 +20169,7 @@
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>1.8800/--</t>
+          <t>1.8800/1.8300</t>
         </is>
       </c>
       <c r="O90" s="3" t="inlineStr">
@@ -19711,7 +20209,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X90" s="3"/>
+      <c r="X90" s="3" t="inlineStr">
+        <is>
+          <t>1.74%~1.84%</t>
+        </is>
+      </c>
       <c r="Y90" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -19891,7 +20393,7 @@
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7950/1.7600</t>
         </is>
       </c>
       <c r="O91" s="3" t="inlineStr">
@@ -19931,7 +20433,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X91" s="3"/>
+      <c r="X91" s="3" t="inlineStr">
+        <is>
+          <t>1.83%~1.93%</t>
+        </is>
+      </c>
       <c r="Y91" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -20111,7 +20617,7 @@
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1600/2.1500</t>
         </is>
       </c>
       <c r="O92" s="3" t="inlineStr">
@@ -20151,7 +20657,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X92" s="3"/>
+      <c r="X92" s="3" t="inlineStr">
+        <is>
+          <t>2.18%~2.28%</t>
+        </is>
+      </c>
       <c r="Y92" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -20553,7 +21063,7 @@
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>1.7600/--</t>
+          <t>1.7600/1.6500</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
@@ -20593,7 +21103,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X94" s="3"/>
+      <c r="X94" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
       <c r="Y94" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -20813,7 +21327,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X95" s="3"/>
+      <c r="X95" s="3" t="inlineStr">
+        <is>
+          <t>1.80%~1.90%</t>
+        </is>
+      </c>
       <c r="Y95" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -21037,7 +21555,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X96" s="3"/>
+      <c r="X96" s="3" t="inlineStr">
+        <is>
+          <t>1.70%~1.80%</t>
+        </is>
+      </c>
       <c r="Y96" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -21257,7 +21779,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X97" s="3"/>
+      <c r="X97" s="3" t="inlineStr">
+        <is>
+          <t>1.63%~1.73%</t>
+        </is>
+      </c>
       <c r="Y97" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -21382,6 +21908,222 @@
         </is>
       </c>
       <c r="AZ97" s="3"/>
+    </row>
+    <row r="98" customHeight="true" ht="18.0">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>26沛兴01</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>10-27 18:00</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>520555.SZ</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K98" s="3"/>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O98" s="3" t="inlineStr">
+        <is>
+          <t>沛县兴田建设投资发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P98" s="3" t="inlineStr">
+        <is>
+          <t>E 0.00</t>
+        </is>
+      </c>
+      <c r="Q98" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="R98" s="3" t="inlineStr">
+        <is>
+          <t>10-27 15:00</t>
+        </is>
+      </c>
+      <c r="S98" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T98" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="U98" s="3"/>
+      <c r="V98" s="3"/>
+      <c r="W98" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X98" s="3"/>
+      <c r="Y98" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z98" s="3"/>
+      <c r="AA98" s="3" t="inlineStr">
+        <is>
+          <t>江苏省-徐州市</t>
+        </is>
+      </c>
+      <c r="AB98" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金扣除发行费用后,拟将3.00亿元用于置换“23沛兴V1”回售偿付的自有资金。[23沛兴V1]</t>
+        </is>
+      </c>
+      <c r="AC98" s="3" t="inlineStr">
+        <is>
+          <t>金元证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD98" s="3" t="inlineStr">
+        <is>
+          <t>江苏省信用增进有限责任公司</t>
+        </is>
+      </c>
+      <c r="AE98" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF98" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG98" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="AH98" s="3" t="inlineStr">
+        <is>
+          <t>沛县兴田建设投资发展集团有限公司2026年面向专业投资者非公开发行公司债券</t>
+        </is>
+      </c>
+      <c r="AI98" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ98" s="3" t="inlineStr">
+        <is>
+          <t>2031-10-28</t>
+        </is>
+      </c>
+      <c r="AK98" s="3"/>
+      <c r="AL98" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM98" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AN98" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AO98" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP98" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ98" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR98" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS98" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT98" s="3" t="inlineStr">
+        <is>
+          <t>房屋建设</t>
+        </is>
+      </c>
+      <c r="AU98" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV98" s="3" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AW98" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX98" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY98" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AZ98" s="3"/>
     </row>
   </sheetData>
   <mergeCells>
